--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="属性（ぞくせい）" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="692">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -1620,34 +1620,37 @@
     <t>せいげん</t>
   </si>
   <si>
+    <t>申請</t>
+  </si>
+  <si>
+    <t>しんせい</t>
+  </si>
+  <si>
+    <t>申請書｜しんせいしょ</t>
+  </si>
+  <si>
+    <t>口ずさみ</t>
+  </si>
+  <si>
+    <t>くちずさみ</t>
+  </si>
+  <si>
+    <t>（哼歌）</t>
+  </si>
+  <si>
+    <t>犠牲</t>
+  </si>
+  <si>
+    <t>ぎせい</t>
+  </si>
+  <si>
+    <t>引用</t>
+  </si>
+  <si>
     <t>協力</t>
   </si>
   <si>
     <t>きょうりょく</t>
-  </si>
-  <si>
-    <t>口ずさみ</t>
-  </si>
-  <si>
-    <t>くちずさみ</t>
-  </si>
-  <si>
-    <t>（哼歌）</t>
-  </si>
-  <si>
-    <t>犠牲</t>
-  </si>
-  <si>
-    <t>ぎせい</t>
-  </si>
-  <si>
-    <t>引用</t>
-  </si>
-  <si>
-    <t>委託</t>
-  </si>
-  <si>
-    <t>いたく</t>
   </si>
   <si>
     <t>視聴</t>
@@ -1691,34 +1694,34 @@
     <t>（左右，支配）</t>
   </si>
   <si>
+    <t>委託</t>
+  </si>
+  <si>
+    <t>いたく</t>
+  </si>
+  <si>
+    <t>開拓</t>
+  </si>
+  <si>
+    <t>かいたく</t>
+  </si>
+  <si>
+    <t>分析</t>
+  </si>
+  <si>
+    <t>ぶんせき</t>
+  </si>
+  <si>
+    <t>更新</t>
+  </si>
+  <si>
+    <t>こうしん</t>
+  </si>
+  <si>
     <t>監督</t>
   </si>
   <si>
     <t>かんとく</t>
-  </si>
-  <si>
-    <t>開拓</t>
-  </si>
-  <si>
-    <t>かいたく</t>
-  </si>
-  <si>
-    <t>分析</t>
-  </si>
-  <si>
-    <t>ぶんせき</t>
-  </si>
-  <si>
-    <t>更新</t>
-  </si>
-  <si>
-    <t>こうしん</t>
-  </si>
-  <si>
-    <t>伝言</t>
-  </si>
-  <si>
-    <t>でんごん</t>
   </si>
   <si>
     <t>出かけ</t>
@@ -1765,28 +1768,55 @@
     <t>せつやく</t>
   </si>
   <si>
+    <t>伝言</t>
+  </si>
+  <si>
+    <t>でんごん</t>
+  </si>
+  <si>
+    <t>実践</t>
+  </si>
+  <si>
+    <t>じっせん</t>
+  </si>
+  <si>
+    <t>達成</t>
+  </si>
+  <si>
+    <t>たっせい</t>
+  </si>
+  <si>
+    <t>収集</t>
+  </si>
+  <si>
+    <t>しゅうしゅう</t>
+  </si>
+  <si>
     <t>通知</t>
   </si>
   <si>
     <t>つうち</t>
   </si>
   <si>
-    <t>実践</t>
-  </si>
-  <si>
-    <t>じっせん</t>
-  </si>
-  <si>
-    <t>達成</t>
-  </si>
-  <si>
-    <t>たっせい</t>
-  </si>
-  <si>
-    <t>収集</t>
-  </si>
-  <si>
-    <t>しゅうしゅう</t>
+    <t>争い</t>
+  </si>
+  <si>
+    <t>あらそい</t>
+  </si>
+  <si>
+    <t>（争吵）</t>
+  </si>
+  <si>
+    <t>回復、恢復</t>
+  </si>
+  <si>
+    <t>かいふ</t>
+  </si>
+  <si>
+    <t>採集</t>
+  </si>
+  <si>
+    <t>さいしゅう</t>
   </si>
   <si>
     <t>干渉</t>
@@ -1795,25 +1825,22 @@
     <t>かんしょう</t>
   </si>
   <si>
-    <t>争い</t>
-  </si>
-  <si>
-    <t>あらそい</t>
-  </si>
-  <si>
-    <t>（争吵）</t>
-  </si>
-  <si>
-    <t>回復、恢復</t>
-  </si>
-  <si>
-    <t>かいふ</t>
-  </si>
-  <si>
-    <t>採集</t>
-  </si>
-  <si>
-    <t>さいしゅう</t>
+    <t>疲れ</t>
+  </si>
+  <si>
+    <t>つかれ</t>
+  </si>
+  <si>
+    <t>公布</t>
+  </si>
+  <si>
+    <t>こうふ</t>
+  </si>
+  <si>
+    <t>操作</t>
+  </si>
+  <si>
+    <t>そうさく</t>
   </si>
   <si>
     <t>補助</t>
@@ -1822,22 +1849,16 @@
     <t>ほじょ</t>
   </si>
   <si>
-    <t>疲れ</t>
-  </si>
-  <si>
-    <t>つかれ</t>
-  </si>
-  <si>
-    <t>公布</t>
-  </si>
-  <si>
-    <t>こうふ</t>
-  </si>
-  <si>
-    <t>操作</t>
-  </si>
-  <si>
-    <t>そうさく</t>
+    <t>行動</t>
+  </si>
+  <si>
+    <t>こうどう</t>
+  </si>
+  <si>
+    <t>（了解）</t>
+  </si>
+  <si>
+    <t>創作</t>
   </si>
   <si>
     <t>領収</t>
@@ -1849,16 +1870,13 @@
     <t>配布資料｜はいふしりょう</t>
   </si>
   <si>
-    <t>行動</t>
-  </si>
-  <si>
-    <t>こうどう</t>
-  </si>
-  <si>
-    <t>（了解）</t>
-  </si>
-  <si>
-    <t>創作</t>
+    <t>了解</t>
+  </si>
+  <si>
+    <t>りょうかい</t>
+  </si>
+  <si>
+    <t>捜索</t>
   </si>
   <si>
     <t>宣伝</t>
@@ -1867,13 +1885,16 @@
     <t>せんでん</t>
   </si>
   <si>
-    <t>了解</t>
-  </si>
-  <si>
-    <t>りょうかい</t>
-  </si>
-  <si>
-    <t>捜索</t>
+    <t>理解</t>
+  </si>
+  <si>
+    <t>りかい</t>
+  </si>
+  <si>
+    <t>探索</t>
+  </si>
+  <si>
+    <t>たんさく</t>
   </si>
   <si>
     <t>配布</t>
@@ -1882,31 +1903,31 @@
     <t>はいふ</t>
   </si>
   <si>
-    <t>理解</t>
-  </si>
-  <si>
-    <t>りかい</t>
-  </si>
-  <si>
-    <t>探索</t>
-  </si>
-  <si>
-    <t>たんさく</t>
+    <t>収蔵</t>
+  </si>
+  <si>
+    <t>しゅうぞう</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>ぶんるい</t>
   </si>
   <si>
     <t>交付</t>
   </si>
   <si>
-    <t>収蔵</t>
-  </si>
-  <si>
-    <t>しゅうぞう</t>
-  </si>
-  <si>
-    <t>分類</t>
-  </si>
-  <si>
-    <t>ぶんるい</t>
+    <t>製作</t>
+  </si>
+  <si>
+    <t>せいさく</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>くぶん</t>
   </si>
   <si>
     <t>保養</t>
@@ -1915,16 +1936,16 @@
     <t>ほよう</t>
   </si>
   <si>
-    <t>製作</t>
-  </si>
-  <si>
-    <t>せいさく</t>
-  </si>
-  <si>
-    <t>区分</t>
-  </si>
-  <si>
-    <t>くぶん</t>
+    <t>制御</t>
+  </si>
+  <si>
+    <t>せいぎょ</t>
+  </si>
+  <si>
+    <t>負担</t>
+  </si>
+  <si>
+    <t>ふたん</t>
   </si>
   <si>
     <t>保留</t>
@@ -1933,16 +1954,16 @@
     <t>ほりゅう</t>
   </si>
   <si>
-    <t>制御</t>
-  </si>
-  <si>
-    <t>せいぎょ</t>
-  </si>
-  <si>
-    <t>負担</t>
-  </si>
-  <si>
-    <t>ふたん</t>
+    <t>評判</t>
+  </si>
+  <si>
+    <t>ひょうばん</t>
+  </si>
+  <si>
+    <t>形容</t>
+  </si>
+  <si>
+    <t>けいよう</t>
   </si>
   <si>
     <t>討論</t>
@@ -1951,16 +1972,16 @@
     <t>とうろん</t>
   </si>
   <si>
-    <t>評判</t>
-  </si>
-  <si>
-    <t>ひょうばん</t>
-  </si>
-  <si>
-    <t>形容</t>
-  </si>
-  <si>
-    <t>けいよう</t>
+    <t>判断</t>
+  </si>
+  <si>
+    <t>はんだん</t>
+  </si>
+  <si>
+    <t>修理</t>
+  </si>
+  <si>
+    <t>しゅうり</t>
   </si>
   <si>
     <t>検討</t>
@@ -1969,16 +1990,16 @@
     <t>けんとう</t>
   </si>
   <si>
-    <t>判断</t>
-  </si>
-  <si>
-    <t>はんだん</t>
-  </si>
-  <si>
-    <t>修理</t>
-  </si>
-  <si>
-    <t>しゅうり</t>
+    <t>判定</t>
+  </si>
+  <si>
+    <t>はんてい</t>
+  </si>
+  <si>
+    <t>修復</t>
+  </si>
+  <si>
+    <t>しゅうふく</t>
   </si>
   <si>
     <t>支持</t>
@@ -1987,16 +2008,10 @@
     <t>しじ</t>
   </si>
   <si>
-    <t>判定</t>
-  </si>
-  <si>
-    <t>はんてい</t>
-  </si>
-  <si>
-    <t>修復</t>
-  </si>
-  <si>
-    <t>しゅうふく</t>
+    <t>創設</t>
+  </si>
+  <si>
+    <t>そうせつ</t>
   </si>
   <si>
     <t>反対</t>
@@ -2005,10 +2020,16 @@
     <t>はんたい</t>
   </si>
   <si>
-    <t>創設</t>
-  </si>
-  <si>
-    <t>そうせつ</t>
+    <t>断定</t>
+  </si>
+  <si>
+    <t>だんてい</t>
+  </si>
+  <si>
+    <t>起動</t>
+  </si>
+  <si>
+    <t>きどう</t>
   </si>
   <si>
     <t>肯定</t>
@@ -2017,16 +2038,16 @@
     <t>こうてい</t>
   </si>
   <si>
-    <t>断定</t>
-  </si>
-  <si>
-    <t>だんてい</t>
-  </si>
-  <si>
-    <t>起動</t>
-  </si>
-  <si>
-    <t>きどう</t>
+    <t>保有</t>
+  </si>
+  <si>
+    <t>ほゆう</t>
+  </si>
+  <si>
+    <t>対処</t>
+  </si>
+  <si>
+    <t>たいしょ</t>
   </si>
   <si>
     <t>否定</t>
@@ -2035,16 +2056,16 @@
     <t>ひてい</t>
   </si>
   <si>
-    <t>保有</t>
-  </si>
-  <si>
-    <t>ほゆう</t>
-  </si>
-  <si>
-    <t>対処</t>
-  </si>
-  <si>
-    <t>たいしょ</t>
+    <t>遵守</t>
+  </si>
+  <si>
+    <t>じゅんしゅ</t>
+  </si>
+  <si>
+    <t>消滅</t>
+  </si>
+  <si>
+    <t>しょうめつ</t>
   </si>
   <si>
     <t>造反</t>
@@ -2053,16 +2074,16 @@
     <t>ぞうはん</t>
   </si>
   <si>
-    <t>遵守</t>
-  </si>
-  <si>
-    <t>じゅんしゅ</t>
-  </si>
-  <si>
-    <t>消滅</t>
-  </si>
-  <si>
-    <t>しょうめつ</t>
+    <t>違反</t>
+  </si>
+  <si>
+    <t>いはん</t>
+  </si>
+  <si>
+    <t>強化</t>
+  </si>
+  <si>
+    <t>きょうか</t>
   </si>
   <si>
     <t>防止</t>
@@ -2071,16 +2092,10 @@
     <t>ぼうし</t>
   </si>
   <si>
-    <t>違反</t>
-  </si>
-  <si>
-    <t>いはん</t>
-  </si>
-  <si>
-    <t>強化</t>
-  </si>
-  <si>
-    <t>きょうか</t>
+    <t>具有</t>
+  </si>
+  <si>
+    <t>ぐゆう</t>
   </si>
   <si>
     <t>接受</t>
@@ -2089,10 +2104,10 @@
     <t>せつじゅ</t>
   </si>
   <si>
-    <t>具有</t>
-  </si>
-  <si>
-    <t>ぐゆう</t>
+    <t>発揮</t>
+  </si>
+  <si>
+    <t>はっき</t>
   </si>
   <si>
     <t>収受</t>
@@ -2101,10 +2116,10 @@
     <t>しゅうじゅ</t>
   </si>
   <si>
-    <t>発揮</t>
-  </si>
-  <si>
-    <t>はっき</t>
+    <t>訓練</t>
+  </si>
+  <si>
+    <t>くんれん</t>
   </si>
   <si>
     <t>解釈</t>
@@ -2113,28 +2128,28 @@
     <t>かいしゃく</t>
   </si>
   <si>
-    <t>訓練</t>
-  </si>
-  <si>
-    <t>くんれん</t>
-  </si>
-  <si>
     <t>告訴</t>
   </si>
   <si>
     <t>こくそ</t>
   </si>
   <si>
+    <t>提出</t>
+  </si>
+  <si>
+    <t>ていしゅつ</t>
+  </si>
+  <si>
     <t>提供</t>
   </si>
   <si>
     <t>ていきょう</t>
   </si>
   <si>
-    <t>提出</t>
-  </si>
-  <si>
-    <t>ていしゅつ</t>
+    <t>主張</t>
+  </si>
+  <si>
+    <t>しゅちょう</t>
   </si>
   <si>
     <t>育成</t>
@@ -2143,10 +2158,10 @@
     <t>いくせい</t>
   </si>
   <si>
-    <t>主張</t>
-  </si>
-  <si>
-    <t>しゅちょう</t>
+    <t>意見</t>
+  </si>
+  <si>
+    <t>いけん</t>
   </si>
   <si>
     <t>接待</t>
@@ -2155,10 +2170,10 @@
     <t>せったい</t>
   </si>
   <si>
-    <t>意見</t>
-  </si>
-  <si>
-    <t>いけん</t>
+    <t>見解</t>
+  </si>
+  <si>
+    <t>けんかい</t>
   </si>
   <si>
     <t>放任</t>
@@ -2167,10 +2182,10 @@
     <t>ほうにん</t>
   </si>
   <si>
-    <t>見解</t>
-  </si>
-  <si>
-    <t>けんかい</t>
+    <t>見方</t>
+  </si>
+  <si>
+    <t>みかた</t>
   </si>
   <si>
     <t>連絡</t>
@@ -2199,10 +2214,10 @@
     </r>
   </si>
   <si>
-    <t>見方</t>
-  </si>
-  <si>
-    <t>みかた</t>
+    <t>確定</t>
+  </si>
+  <si>
+    <t>かくてい</t>
   </si>
   <si>
     <t>抜擢</t>
@@ -2211,10 +2226,10 @@
     <t>ばってき</t>
   </si>
   <si>
-    <t>確定</t>
-  </si>
-  <si>
-    <t>かくてい</t>
+    <t>祈禱</t>
+  </si>
+  <si>
+    <t>きとう</t>
   </si>
   <si>
     <t>心配</t>
@@ -2223,10 +2238,10 @@
     <t>しんぱい</t>
   </si>
   <si>
-    <t>祈禱</t>
-  </si>
-  <si>
-    <t>きとう</t>
+    <t>進化</t>
+  </si>
+  <si>
+    <t>しんか</t>
   </si>
   <si>
     <t>報告</t>
@@ -2235,10 +2250,10 @@
     <t>ほうこく</t>
   </si>
   <si>
-    <t>進化</t>
-  </si>
-  <si>
-    <t>しんか</t>
+    <t>実施</t>
+  </si>
+  <si>
+    <t>じっし</t>
   </si>
   <si>
     <t>競争</t>
@@ -2247,22 +2262,16 @@
     <t>きょうそう</t>
   </si>
   <si>
-    <t>実施</t>
-  </si>
-  <si>
-    <t>じっし</t>
+    <t>承認</t>
+  </si>
+  <si>
+    <t>しょうにん</t>
   </si>
   <si>
     <t>援助</t>
   </si>
   <si>
     <t>えんじょ</t>
-  </si>
-  <si>
-    <t>承認</t>
-  </si>
-  <si>
-    <t>しょうにん</t>
   </si>
   <si>
     <t>応援</t>
@@ -4950,7 +4959,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
@@ -5161,204 +5170,204 @@
       <c r="K7" s="1" t="s">
         <v>475</v>
       </c>
+      <c r="L7" s="1" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>377</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>456</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="L14" s="1" t="s">
         <v>535</v>
       </c>
     </row>
@@ -5382,7 +5391,7 @@
         <v>539</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>540</v>
@@ -5390,165 +5399,168 @@
       <c r="K15" s="1" t="s">
         <v>541</v>
       </c>
+      <c r="L15" s="1" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="16" spans="1:15">
       <c r="D16" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>530</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="4:11">
@@ -5559,216 +5571,213 @@
         <v>147</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33" spans="4:12">
       <c r="D33" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="34" spans="4:12">
       <c r="D34" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="L36" s="1" t="s">
         <v>646</v>
       </c>
     </row>
@@ -5785,155 +5794,166 @@
       <c r="K37" s="1" t="s">
         <v>650</v>
       </c>
+      <c r="L37" s="1" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="43" spans="4:12">
       <c r="J43" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="44" spans="4:12">
       <c r="J44" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="45" spans="4:12">
       <c r="J45" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="46" spans="4:12">
       <c r="J46" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="49" spans="10:11">
       <c r="J49" s="1" t="s">
-        <v>570</v>
+        <v>684</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>571</v>
+        <v>685</v>
       </c>
     </row>
     <row r="50" spans="10:11">
       <c r="J50" s="1" t="s">
-        <v>683</v>
+        <v>571</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>684</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="10:11">
       <c r="J51" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="52" spans="10:11">
       <c r="J52" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11">
+      <c r="J53" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>

--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="706">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -525,6 +525,18 @@
     <t>えんぎ</t>
   </si>
   <si>
+    <t>原則</t>
+  </si>
+  <si>
+    <t>げんそく</t>
+  </si>
+  <si>
+    <t>目方</t>
+  </si>
+  <si>
+    <t>めかた</t>
+  </si>
+  <si>
     <t>病み</t>
   </si>
   <si>
@@ -2110,6 +2122,12 @@
     <t>はっき</t>
   </si>
   <si>
+    <t>修正</t>
+  </si>
+  <si>
+    <t>しゅうせい</t>
+  </si>
+  <si>
     <t>収受</t>
   </si>
   <si>
@@ -2333,6 +2351,47 @@
   <si>
     <t>たいせん</t>
   </si>
+  <si>
+    <t>勝ち負け</t>
+  </si>
+  <si>
+    <t>かちまけ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>输赢）</t>
+    </r>
+  </si>
+  <si>
+    <t>求婚</t>
+  </si>
+  <si>
+    <t>きゅうこん</t>
+  </si>
+  <si>
+    <t>投書</t>
+  </si>
+  <si>
+    <t>とうしょ</t>
+  </si>
+  <si>
+    <t>（投稿）</t>
+  </si>
 </sst>
 </file>
 
@@ -2344,7 +2403,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2532,6 +2591,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -3313,7 +3378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3786,6 +3851,25 @@
       </c>
       <c r="E39" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="4:6">
+      <c r="D40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="4:6">
+      <c r="D41" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" t="s">
+        <v>131</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3811,432 +3895,432 @@
   <sheetData>
     <row r="1" ht="18" spans="1:11">
       <c r="G1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:11">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:8">
       <c r="G21" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:8">
       <c r="G22" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:8">
       <c r="G23" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:8">
       <c r="G24" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:8">
       <c r="G25" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:8">
       <c r="G26" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:8">
       <c r="G27" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:8">
       <c r="G28" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:8">
       <c r="G29" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:8">
       <c r="G30" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:8">
       <c r="G31" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:8">
       <c r="G32" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" ht="18" spans="7:8">
       <c r="G33" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" ht="18" spans="7:8">
       <c r="G34" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="7:8">
       <c r="G35" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H35" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4257,18 +4341,18 @@
   <sheetData>
     <row r="1" ht="18" spans="1:5">
       <c r="A1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>61</v>
@@ -4279,411 +4363,411 @@
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C6" s="7"/>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" ht="17.4" customHeight="1" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" ht="36" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:3">
       <c r="A41" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:3">
       <c r="A43" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -4705,249 +4789,249 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F9" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C20" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C21" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -4959,7 +5043,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
@@ -4973,410 +5057,410 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>97</v>
@@ -5385,575 +5469,619 @@
         <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="D16" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="24" spans="4:11">
       <c r="D24" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>628</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="33" spans="4:12">
       <c r="D33" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="34" spans="4:12">
       <c r="D34" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="4:12">
       <c r="D37" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="43" spans="4:12">
       <c r="J43" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="44" spans="4:12">
       <c r="J44" s="1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="45" spans="4:12">
       <c r="J45" s="1" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="46" spans="4:12">
       <c r="J46" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="49" spans="10:12">
       <c r="J49" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="50" spans="10:12">
       <c r="J50" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="51" spans="10:12">
       <c r="J51" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="52" spans="10:12">
       <c r="J52" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="53" spans="10:12">
       <c r="J53" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="54" spans="10:12">
+      <c r="J54" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>691</v>
+      </c>
+    </row>
+    <row r="55" spans="10:12">
+      <c r="J55" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="56" spans="10:12">
+      <c r="J56" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="57" spans="10:12">
+      <c r="J57" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="属性（ぞくせい）" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="716">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -891,6 +891,12 @@
     <t>かんせん</t>
   </si>
   <si>
+    <t>傷口</t>
+  </si>
+  <si>
+    <t>きずぐち</t>
+  </si>
+  <si>
     <t>首</t>
   </si>
   <si>
@@ -2140,6 +2146,12 @@
     <t>くんれん</t>
   </si>
   <si>
+    <t>朗読</t>
+  </si>
+  <si>
+    <t>ろうどく</t>
+  </si>
+  <si>
     <t>解釈</t>
   </si>
   <si>
@@ -2292,6 +2304,9 @@
     <t>えんじょ</t>
   </si>
   <si>
+    <t>健闘</t>
+  </si>
+  <si>
     <t>応援</t>
   </si>
   <si>
@@ -2391,6 +2406,21 @@
   </si>
   <si>
     <t>（投稿）</t>
+  </si>
+  <si>
+    <t>考査</t>
+  </si>
+  <si>
+    <t>こうさ</t>
+  </si>
+  <si>
+    <t>考察</t>
+  </si>
+  <si>
+    <t>奨励</t>
+  </si>
+  <si>
+    <t>しょうれい</t>
   </si>
 </sst>
 </file>
@@ -3882,7 +3912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="11.6666666666667" customWidth="1"/>
@@ -4321,6 +4351,14 @@
       </c>
       <c r="H35" t="s">
         <v>249</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8">
+      <c r="G36" t="s">
+        <v>250</v>
+      </c>
+      <c r="H36" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4341,18 +4379,18 @@
   <sheetData>
     <row r="1" ht="18" spans="1:5">
       <c r="A1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>61</v>
@@ -4363,72 +4401,72 @@
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C6" s="7"/>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>193</v>
@@ -4436,244 +4474,244 @@
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" ht="17.4" customHeight="1" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" ht="36" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>247</v>
@@ -4681,93 +4719,93 @@
     </row>
     <row r="40" ht="54" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:3">
       <c r="A41" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:3">
       <c r="A43" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4789,249 +4827,249 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C20" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C21" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -5043,7 +5081,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
@@ -5057,115 +5095,115 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>248</v>
@@ -5176,291 +5214,291 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>97</v>
@@ -5469,182 +5507,182 @@
         <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="D16" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="24" spans="4:11">
@@ -5655,433 +5693,477 @@
         <v>151</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>636</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="33" spans="4:12">
       <c r="D33" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="34" spans="4:12">
       <c r="D34" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="37" spans="4:12">
       <c r="D37" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="43" spans="4:12">
+      <c r="D43" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>588</v>
+      </c>
       <c r="J43" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="44" spans="4:12">
       <c r="J44" s="1" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" spans="4:12">
       <c r="J45" s="1" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="46" spans="4:12">
       <c r="J46" s="1" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="49" spans="10:12">
       <c r="J49" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" spans="10:12">
       <c r="J50" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="51" spans="10:12">
       <c r="J51" s="1" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="52" spans="10:12">
       <c r="J52" s="1" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="53" spans="10:12">
       <c r="J53" s="1" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="54" spans="10:12">
       <c r="J54" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="55" spans="10:12">
       <c r="J55" s="1" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="56" spans="10:12">
       <c r="J56" s="1" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="57" spans="10:12">
       <c r="J57" s="1" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>705</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="58" spans="10:12">
+      <c r="J58" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="59" spans="10:12">
+      <c r="J59" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="60" spans="10:12">
+      <c r="J60" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="61" spans="10:12">
+      <c r="J61" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>715</v>
       </c>
     </row>
   </sheetData>

--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="属性（ぞくせい）" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="726">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -609,6 +609,12 @@
     <t>ふにんちりょ</t>
   </si>
   <si>
+    <t>負傷</t>
+  </si>
+  <si>
+    <t>ふしょう</t>
+  </si>
+  <si>
     <t>治療</t>
   </si>
   <si>
@@ -2158,6 +2164,12 @@
     <t>かいしゃく</t>
   </si>
   <si>
+    <t>防犯</t>
+  </si>
+  <si>
+    <t>ぼうはん</t>
+  </si>
+  <si>
     <t>告訴</t>
   </si>
   <si>
@@ -2313,10 +2325,22 @@
     <t>おうえん</t>
   </si>
   <si>
+    <t>反省</t>
+  </si>
+  <si>
+    <t>はんせい</t>
+  </si>
+  <si>
     <t>期待</t>
   </si>
   <si>
     <t>きたい</t>
+  </si>
+  <si>
+    <t>影響</t>
+  </si>
+  <si>
+    <t>えいきょう</t>
   </si>
   <si>
     <t>抵抗</t>
@@ -2421,6 +2445,12 @@
   </si>
   <si>
     <t>しょうれい</t>
+  </si>
+  <si>
+    <t>送別</t>
+  </si>
+  <si>
+    <t>そうべつ</t>
   </si>
 </sst>
 </file>
@@ -4002,363 +4032,369 @@
       <c r="H4" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="J4" t="s">
+        <v>156</v>
+      </c>
+      <c r="K4" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="5" ht="18" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:11">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:8">
       <c r="G21" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:8">
       <c r="G22" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:8">
       <c r="G23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:8">
       <c r="G24" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:8">
       <c r="G25" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:8">
       <c r="G26" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:8">
       <c r="G27" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:8">
       <c r="G28" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:8">
       <c r="G29" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:8">
       <c r="G30" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:8">
       <c r="G31" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:8">
       <c r="G32" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" ht="18" spans="7:8">
       <c r="G33" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" ht="18" spans="7:8">
       <c r="G34" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="7:8">
       <c r="G35" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H35" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="7:8">
       <c r="G36" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -4379,18 +4415,18 @@
   <sheetData>
     <row r="1" ht="18" spans="1:5">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>61</v>
@@ -4401,411 +4437,411 @@
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C6" s="7"/>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" ht="17.4" customHeight="1" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" ht="36" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:3">
       <c r="A41" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:3">
       <c r="A43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -4827,249 +4863,249 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C20" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C21" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -5081,7 +5117,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
@@ -5095,410 +5131,410 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>97</v>
@@ -5507,182 +5543,182 @@
         <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="D16" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="24" spans="4:11">
@@ -5693,477 +5729,517 @@
         <v>151</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="33" spans="4:12">
       <c r="D33" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34" spans="4:12">
       <c r="D34" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="37" spans="4:12">
       <c r="D37" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43" spans="4:12">
       <c r="D43" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" spans="4:12">
+      <c r="D44" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>690</v>
+      </c>
       <c r="J44" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="45" spans="4:12">
+      <c r="D45" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>694</v>
+      </c>
       <c r="J45" s="1" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
     </row>
     <row r="46" spans="4:12">
       <c r="J46" s="1" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
     </row>
     <row r="49" spans="10:12">
       <c r="J49" s="1" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
     </row>
     <row r="50" spans="10:12">
       <c r="J50" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="51" spans="10:12">
       <c r="J51" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="52" spans="10:12">
       <c r="J52" s="1" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
     </row>
     <row r="53" spans="10:12">
       <c r="J53" s="1" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
     </row>
     <row r="54" spans="10:12">
       <c r="J54" s="1" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
     </row>
     <row r="55" spans="10:12">
       <c r="J55" s="1" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
     </row>
     <row r="56" spans="10:12">
       <c r="J56" s="1" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
     </row>
     <row r="57" spans="10:12">
       <c r="J57" s="1" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
     <row r="58" spans="10:12">
       <c r="J58" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="59" spans="10:12">
       <c r="J59" s="1" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
     </row>
     <row r="60" spans="10:12">
       <c r="J60" s="1" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
     </row>
     <row r="61" spans="10:12">
       <c r="J61" s="1" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>715</v>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="62" spans="10:12">
+      <c r="J62" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="63" spans="10:12">
+      <c r="J63" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>725</v>
       </c>
     </row>
   </sheetData>

--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="728">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -2192,6 +2192,12 @@
   </si>
   <si>
     <t>しゅちょう</t>
+  </si>
+  <si>
+    <t>解決</t>
+  </si>
+  <si>
+    <t>かいけつ</t>
   </si>
   <si>
     <t>育成</t>
@@ -5928,200 +5934,206 @@
       <c r="E34" s="1" t="s">
         <v>650</v>
       </c>
+      <c r="G34" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>652</v>
+      </c>
       <c r="J34" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="37" spans="4:12">
       <c r="D37" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="43" spans="4:12">
       <c r="D43" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>590</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="44" spans="4:12">
       <c r="D44" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="4:12">
       <c r="D45" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="46" spans="4:12">
       <c r="J46" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="49" spans="10:12">
       <c r="J49" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="50" spans="10:12">
@@ -6134,64 +6146,64 @@
     </row>
     <row r="51" spans="10:12">
       <c r="J51" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="52" spans="10:12">
       <c r="J52" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="53" spans="10:12">
       <c r="J53" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="54" spans="10:12">
       <c r="J54" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="55" spans="10:12">
       <c r="J55" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="56" spans="10:12">
       <c r="J56" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="57" spans="10:12">
       <c r="J57" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="58" spans="10:12">
@@ -6204,26 +6216,26 @@
     </row>
     <row r="59" spans="10:12">
       <c r="J59" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="60" spans="10:12">
       <c r="J60" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="61" spans="10:12">
       <c r="J61" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="62" spans="10:12">
@@ -6236,10 +6248,10 @@
     </row>
     <row r="63" spans="10:12">
       <c r="J63" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>

--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="属性（ぞくせい）" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="729">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -1261,6 +1261,9 @@
   </si>
   <si>
     <t>ちのう</t>
+  </si>
+  <si>
+    <t>知能検査｜ちのうけんさ</t>
   </si>
   <si>
     <t>堕胎</t>
@@ -4883,203 +4886,206 @@
       <c r="G2" s="1" t="s">
         <v>363</v>
       </c>
+      <c r="H2" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
@@ -5092,26 +5098,26 @@
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C20" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -5137,115 +5143,115 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>250</v>
@@ -5256,291 +5262,291 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>97</v>
@@ -5549,182 +5555,182 @@
         <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="D16" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="24" spans="4:11">
@@ -5735,523 +5741,529 @@
         <v>151</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="33" spans="4:12">
       <c r="D33" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="4:12">
       <c r="D34" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="37" spans="4:12">
       <c r="D37" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="43" spans="4:12">
       <c r="D43" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="44" spans="4:12">
       <c r="D44" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45" spans="4:12">
       <c r="D45" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="46" spans="4:12">
+      <c r="D46" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>631</v>
+      </c>
       <c r="J46" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="49" spans="10:12">
       <c r="J49" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="50" spans="10:12">
       <c r="J50" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="51" spans="10:12">
       <c r="J51" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="52" spans="10:12">
       <c r="J52" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="53" spans="10:12">
       <c r="J53" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="54" spans="10:12">
       <c r="J54" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="55" spans="10:12">
       <c r="J55" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="56" spans="10:12">
       <c r="J56" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="57" spans="10:12">
       <c r="J57" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="58" spans="10:12">
       <c r="J58" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="59" spans="10:12">
       <c r="J59" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="60" spans="10:12">
       <c r="J60" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="61" spans="10:12">
       <c r="J61" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="62" spans="10:12">
       <c r="J62" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="63" spans="10:12">
       <c r="J63" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>

--- a/身体（からだ）.xlsx
+++ b/身体（からだ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="属性（ぞくせい）" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="736">
   <si>
     <t>固有属性｜こゆうぞくせい</t>
   </si>
@@ -537,6 +537,15 @@
     <t>めかた</t>
   </si>
   <si>
+    <t>口振り</t>
+  </si>
+  <si>
+    <t>くちぶり</t>
+  </si>
+  <si>
+    <t>说话时的语气</t>
+  </si>
+  <si>
     <t>病み</t>
   </si>
   <si>
@@ -901,6 +910,12 @@
   </si>
   <si>
     <t>きずぐち</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>ちゅうどく</t>
   </si>
   <si>
     <t>首</t>
@@ -2237,6 +2252,12 @@
   </si>
   <si>
     <t>みかた</t>
+  </si>
+  <si>
+    <t>公表</t>
+  </si>
+  <si>
+    <t>こうひょう</t>
   </si>
   <si>
     <t>連絡</t>
@@ -3447,7 +3468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3939,6 +3960,17 @@
       </c>
       <c r="F41" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="4:6">
+      <c r="D42" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3951,7 +3983,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="11.6666666666667" customWidth="1"/>
@@ -3964,446 +3996,454 @@
   <sheetData>
     <row r="1" ht="18" spans="1:11">
       <c r="G1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:11">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:8">
       <c r="G21" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:8">
       <c r="G22" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:8">
       <c r="G23" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:8">
       <c r="G24" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:8">
       <c r="G25" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:8">
       <c r="G26" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:8">
       <c r="G27" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:8">
       <c r="G28" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:8">
       <c r="G29" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:8">
       <c r="G30" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:8">
       <c r="G31" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:8">
       <c r="G32" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" ht="18" spans="7:8">
       <c r="G33" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" ht="18" spans="7:8">
       <c r="G34" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="7:8">
       <c r="G35" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="7:8">
       <c r="G36" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H36" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8">
+      <c r="G37" t="s">
+        <v>257</v>
+      </c>
+      <c r="H37" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4424,18 +4464,18 @@
   <sheetData>
     <row r="1" ht="18" spans="1:5">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>61</v>
@@ -4446,411 +4486,411 @@
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C6" s="7"/>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" ht="17.4" customHeight="1" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" ht="36" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:3">
       <c r="A41" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:3">
       <c r="A43" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -4872,252 +4912,252 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="H4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F9" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="5" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C20" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C21" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -5143,410 +5183,410 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>97</v>
@@ -5555,715 +5595,733 @@
         <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="J15" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="D16" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="4:11">
       <c r="D17" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="18" spans="4:11">
       <c r="D18" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" spans="4:11">
       <c r="D19" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="4:11">
       <c r="D20" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="21" spans="4:11">
       <c r="D21" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="22" spans="4:11">
       <c r="D22" s="1" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="23" spans="4:11">
       <c r="D23" s="1" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" spans="4:11">
       <c r="D24" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="4:11">
       <c r="D25" s="1" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="4:11">
       <c r="D26" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27" spans="4:11">
       <c r="D27" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="28" spans="4:11">
       <c r="D28" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="29" spans="4:11">
       <c r="D29" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="30" spans="4:11">
       <c r="D30" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="4:11">
       <c r="D31" s="1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="32" spans="4:11">
       <c r="D32" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" spans="4:12">
       <c r="D33" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="34" spans="4:12">
       <c r="D34" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="35" spans="4:12">
       <c r="D35" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>657</v>
+        <v>662</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>561</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="36" spans="4:12">
       <c r="D36" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>661</v>
+        <v>666</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>598</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="37" spans="4:12">
       <c r="D37" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>665</v>
+        <v>670</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>672</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="38" spans="4:12">
       <c r="D38" s="1" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
     </row>
     <row r="39" spans="4:12">
       <c r="D39" s="1" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
     </row>
     <row r="40" spans="4:12">
       <c r="D40" s="1" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="41" spans="4:12">
       <c r="D41" s="1" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="42" spans="4:12">
       <c r="D42" s="1" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="43" spans="4:12">
       <c r="D43" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="44" spans="4:12">
       <c r="D44" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="45" spans="4:12">
       <c r="D45" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
     <row r="46" spans="4:12">
       <c r="D46" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="47" spans="4:12">
       <c r="J47" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
     </row>
     <row r="48" spans="4:12">
       <c r="J48" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="49" spans="10:12">
       <c r="J49" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="50" spans="10:12">
       <c r="J50" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="51" spans="10:12">
       <c r="J51" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
     </row>
     <row r="52" spans="10:12">
       <c r="J52" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="53" spans="10:12">
       <c r="J53" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="54" spans="10:12">
       <c r="J54" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="55" spans="10:12">
       <c r="J55" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="56" spans="10:12">
       <c r="J56" s="1" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
     </row>
     <row r="57" spans="10:12">
       <c r="J57" s="1" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="58" spans="10:12">
       <c r="J58" s="1" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="59" spans="10:12">
       <c r="J59" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="60" spans="10:12">
       <c r="J60" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="61" spans="10:12">
       <c r="J61" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="62" spans="10:12">
       <c r="J62" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="63" spans="10:12">
       <c r="J63" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
